--- a/assessment_forms/005_medical_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/005_medical_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
